--- a/content/A2-محتوا.xlsx
+++ b/content/A2-محتوا.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>موضوع محتوایی</t>
+          <t>ماموریت درس</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>روتین روزانه در سطح بالاتر</t>
+          <t>روتینت را طبیعی‌تر تعریف کن</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>خانه و کارهای همزمان</t>
+          <t>فرق کار همیشگی و همین حالا</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>خاطرات</t>
+          <t>خاطره‌ها را بهتر تعریف کن</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>قطع شدن یک کار</t>
+          <t>وقتی یک اتفاق وسط کار افتاد</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>تعریف کردن یک ماجرا</t>
+          <t>یک ماجرا را جذاب تعریف کن</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>قول دادن و پیشنهاد</t>
+          <t>قول بده و پیشنهاد بده</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>قرار گذاشتن</t>
+          <t>برای یک قرار واقعی هماهنگ کن</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>پیش‌بینی و تردید</t>
+          <t>احتمال بده و حدس بزن</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی با شرط</t>
+          <t>اگر شد… برنامه‌ات چیست؟</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>برنامه‌های گروهی</t>
+          <t>با بقیه برنامه بچین</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>خرید و مقایسه</t>
+          <t>قیمت و گزینه‌ها را مقایسه کن</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>چگونه کاری انجام می‌شود</t>
+          <t>بگو کاری چطور انجام می‌شود</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>مقایسه برابر</t>
+          <t>بگو چقدر شبیه یا متفاوت‌اند</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>مدت زمان</t>
+          <t>بگو از کی و چه مدت</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>تجربه‌های زندگی</t>
+          <t>از تجربه‌های زندگی بپرس</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>کارهای تمام‌شده</t>
+          <t>بگو چه کاری انجام شده</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>تفاوت دو زمان</t>
+          <t>زمان درست را انتخاب کن</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>توصیف اشیا و فرایندها</t>
+          <t>بگو چیزی کجا و چطور ساخته شده</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>توصیف افراد و چیزها</t>
+          <t>آدم‌ها و چیزها را دقیق‌تر توصیف کن</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>روایت بلندتر</t>
+          <t>یک داستان کامل‌تر تعریف کن</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>توصیه و الزام</t>
+          <t>توصیه کن و از الزام بگو</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>قوانین و علائم</t>
+          <t>قانون‌ها و تابلوها را بفهم</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>درخواست در موقعیت رسمی</t>
+          <t>محترمانه درخواست کن</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>هتل و رزرو</t>
+          <t>هتل رزرو کن و درخواست بده</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>موقعیت پزشکی</t>
+          <t>در موقعیت پزشکی حرف بزن</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>علاقه و تصمیم</t>
+          <t>از علاقه و تصمیم حرف بزن</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>بازگو کردن حرف دیگران</t>
+          <t>حرف دیگران را بازگو کن</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>کمبود و زیادی</t>
+          <t>بگو خیلی زیاد است یا کافی نیست</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>چیزهای نامشخص</t>
+          <t>درباره چیزهای نامشخص حرف بزن</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>جمع‌بندی سطح</t>
+          <t>A2 تمام؛ آماده مرحله بعد</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">

--- a/content/A2-محتوا.xlsx
+++ b/content/A2-محتوا.xlsx
@@ -47605,7 +47605,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -47997,7 +47997,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -48385,7 +48385,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -48769,7 +48769,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -49153,7 +49153,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -49549,7 +49549,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -49937,7 +49937,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -50325,7 +50325,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -50713,7 +50713,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -51105,7 +51105,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -51489,7 +51489,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -51873,7 +51873,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -52257,7 +52257,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -52641,7 +52641,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -53029,7 +53029,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -53417,7 +53417,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -53801,7 +53801,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -54185,7 +54185,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -54573,7 +54573,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -54957,7 +54957,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -55345,7 +55345,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -55729,7 +55729,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -56121,7 +56121,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -56509,7 +56509,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -56893,7 +56893,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -57277,7 +57277,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -57665,7 +57665,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -58049,7 +58049,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -58437,7 +58437,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -58825,7 +58825,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>جمله را واضح تلفظ کنید.</t>
+          <t>جمله را واضح تلفظ کن.</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
